--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1896-1901.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1896-1901.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D768233A-D18C-45D5-800D-CA3215F62935}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CDAF5B-7131-4A6E-B0FC-B8C162227C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="95925" yWindow="240" windowWidth="18975" windowHeight="22905" activeTab="1" xr2:uid="{612ECE8A-2482-4A8D-B910-9BB68D33C7AD}"/>
+    <workbookView xWindow="67020" yWindow="3960" windowWidth="39795" windowHeight="13170" activeTab="1" xr2:uid="{612ECE8A-2482-4A8D-B910-9BB68D33C7AD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -618,7 +618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -639,10 +639,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -661,9 +657,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -701,7 +697,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -807,7 +803,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -949,7 +945,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -15649,13 +15645,13 @@
       <c r="B325" s="6">
         <v>1901</v>
       </c>
-      <c r="C325" s="12">
+      <c r="C325" s="5">
         <v>1562106</v>
       </c>
-      <c r="D325" s="12">
+      <c r="D325" s="5">
         <v>67123</v>
       </c>
-      <c r="E325" s="12">
+      <c r="E325" s="5">
         <v>37971</v>
       </c>
     </row>
@@ -15666,13 +15662,13 @@
       <c r="B326" s="6">
         <v>1896</v>
       </c>
-      <c r="C326" s="13">
+      <c r="C326" s="8">
         <v>2715265</v>
       </c>
-      <c r="D326" s="12">
+      <c r="D326" s="5">
         <v>144989</v>
       </c>
-      <c r="E326" s="12">
+      <c r="E326" s="5">
         <v>94155</v>
       </c>
     </row>
@@ -15680,13 +15676,13 @@
       <c r="B327" s="6">
         <v>1897</v>
       </c>
-      <c r="C327" s="13">
+      <c r="C327" s="8">
         <v>2769204</v>
       </c>
-      <c r="D327" s="12">
+      <c r="D327" s="5">
         <v>148253</v>
       </c>
-      <c r="E327" s="12">
+      <c r="E327" s="5">
         <v>90037</v>
       </c>
     </row>
@@ -15694,13 +15690,13 @@
       <c r="B328" s="6">
         <v>1898</v>
       </c>
-      <c r="C328" s="12">
+      <c r="C328" s="5">
         <v>3011523</v>
       </c>
-      <c r="D328" s="12">
+      <c r="D328" s="5">
         <v>139331</v>
       </c>
-      <c r="E328" s="12">
+      <c r="E328" s="5">
         <v>111021</v>
       </c>
     </row>
@@ -15708,13 +15704,13 @@
       <c r="B329" s="6">
         <v>1899</v>
       </c>
-      <c r="C329" s="12">
+      <c r="C329" s="5">
         <v>3085873</v>
       </c>
-      <c r="D329" s="12">
+      <c r="D329" s="5">
         <v>148152</v>
       </c>
-      <c r="E329" s="13">
+      <c r="E329" s="8">
         <v>86606</v>
       </c>
     </row>
@@ -15722,13 +15718,13 @@
       <c r="B330" s="6">
         <v>1900</v>
       </c>
-      <c r="C330" s="12">
+      <c r="C330" s="5">
         <v>3149625</v>
       </c>
-      <c r="D330" s="13">
+      <c r="D330" s="8">
         <v>155565</v>
       </c>
-      <c r="E330" s="12">
+      <c r="E330" s="5">
         <v>91358</v>
       </c>
     </row>
@@ -15736,13 +15732,13 @@
       <c r="B331" s="6">
         <v>1901</v>
       </c>
-      <c r="C331" s="12">
+      <c r="C331" s="5">
         <v>3161116</v>
       </c>
-      <c r="D331" s="12">
+      <c r="D331" s="5">
         <v>155877</v>
       </c>
-      <c r="E331" s="12">
+      <c r="E331" s="5">
         <v>107068</v>
       </c>
     </row>
@@ -15753,13 +15749,13 @@
       <c r="B332" s="6">
         <v>1896</v>
       </c>
-      <c r="C332" s="13">
+      <c r="C332" s="8">
         <v>1912559</v>
       </c>
-      <c r="D332" s="12">
+      <c r="D332" s="5">
         <v>88178</v>
       </c>
-      <c r="E332" s="12">
+      <c r="E332" s="5">
         <v>66574</v>
       </c>
     </row>
@@ -15770,10 +15766,10 @@
       <c r="C333" s="10">
         <v>1976494</v>
       </c>
-      <c r="D333" s="12">
+      <c r="D333" s="5">
         <v>89815</v>
       </c>
-      <c r="E333" s="12">
+      <c r="E333" s="5">
         <v>64180</v>
       </c>
     </row>
@@ -15781,13 +15777,13 @@
       <c r="B334" s="6">
         <v>1898</v>
       </c>
-      <c r="C334" s="12">
+      <c r="C334" s="5">
         <v>2043290</v>
       </c>
-      <c r="D334" s="12">
+      <c r="D334" s="5">
         <v>90233</v>
       </c>
-      <c r="E334" s="12">
+      <c r="E334" s="5">
         <v>65455</v>
       </c>
     </row>
@@ -15798,10 +15794,10 @@
       <c r="C335" s="10">
         <v>2079665</v>
       </c>
-      <c r="D335" s="12">
+      <c r="D335" s="5">
         <v>94327</v>
       </c>
-      <c r="E335" s="12">
+      <c r="E335" s="5">
         <v>56952</v>
       </c>
     </row>
@@ -15809,10 +15805,10 @@
       <c r="B336" s="6">
         <v>1900</v>
       </c>
-      <c r="C336" s="12">
+      <c r="C336" s="5">
         <v>2104704</v>
       </c>
-      <c r="D336" s="12">
+      <c r="D336" s="5">
         <v>92374</v>
       </c>
       <c r="E336" s="8">
@@ -15823,13 +15819,13 @@
       <c r="B337" s="6">
         <v>1901</v>
       </c>
-      <c r="C337" s="12">
+      <c r="C337" s="5">
         <v>2117891</v>
       </c>
-      <c r="D337" s="12">
+      <c r="D337" s="5">
         <v>93133</v>
       </c>
-      <c r="E337" s="12">
+      <c r="E337" s="5">
         <v>79946</v>
       </c>
     </row>
@@ -15843,7 +15839,7 @@
       <c r="C338" s="8">
         <v>1431322</v>
       </c>
-      <c r="D338" s="12">
+      <c r="D338" s="5">
         <v>83327</v>
       </c>
       <c r="E338" s="8">
@@ -16135,8 +16131,8 @@
       <c r="D358" s="5">
         <v>116575</v>
       </c>
-      <c r="E358" s="5">
-        <v>93696</v>
+      <c r="E358" s="9">
+        <v>63696</v>
       </c>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -16149,8 +16145,8 @@
       <c r="D359" s="5">
         <v>121212</v>
       </c>
-      <c r="E359" s="9">
-        <v>63696</v>
+      <c r="E359" s="5">
+        <v>69388</v>
       </c>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.55000000000000004">
@@ -17493,7 +17489,7 @@
       <c r="B452" s="6">
         <v>1896</v>
       </c>
-      <c r="C452" s="13">
+      <c r="C452" s="8">
         <v>789191</v>
       </c>
       <c r="D452" s="5">
@@ -17507,7 +17503,7 @@
       <c r="B453" s="6">
         <v>1897</v>
       </c>
-      <c r="C453" s="13">
+      <c r="C453" s="8">
         <v>808089</v>
       </c>
       <c r="D453" s="5">
@@ -20088,4 +20084,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>